--- a/gte/nodes/P/compressor_stage_1_blade_stator_coordinates_foil.xlsx
+++ b/gte/nodes/P/compressor_stage_1_blade_stator_coordinates_foil.xlsx
@@ -349,7 +349,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0.00021446783904443271</v>
+        <v>0.00016085087928327161</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -357,7 +357,7 @@
         <v>0.002978719986728232</v>
       </c>
       <c r="B2">
-        <v>0.0011306079739885032</v>
+        <v>0.00096971324233004923</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.005957439973456464</v>
       </c>
       <c r="B3">
-        <v>0.0019867312002038633</v>
+        <v>0.0017272456199235941</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0089361599601846965</v>
       </c>
       <c r="B4">
-        <v>0.0027924602320345817</v>
+        <v>0.0024406754098632711</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.011914879946912928</v>
       </c>
       <c r="B5">
-        <v>0.0035574177838247241</v>
+        <v>0.0031172300099484465</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.01489359993364116</v>
       </c>
       <c r="B6">
-        <v>0.0042872345243894355</v>
+        <v>0.0037611426085817569</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.017872319920369393</v>
       </c>
       <c r="B7">
-        <v>0.0049715729404281621</v>
+        <v>0.0043646695565789269</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.020851039907097624</v>
       </c>
       <c r="B8">
-        <v>0.0055995240587512762</v>
+        <v>0.004919638330884761</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.023829759893825856</v>
       </c>
       <c r="B9">
-        <v>0.0061738612487285682</v>
+        <v>0.00542813775054732</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.026808479880554088</v>
       </c>
       <c r="B10">
-        <v>0.0066998033217428527</v>
+        <v>0.0058940902962658394</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.029787199867282319</v>
       </c>
       <c r="B11">
-        <v>0.00717866851466963</v>
+        <v>0.0063184917532410146</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.032765919854010554</v>
       </c>
       <c r="B12">
-        <v>0.00761079992075757</v>
+        <v>0.0067016062327989083</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.035744639840738786</v>
       </c>
       <c r="B13">
-        <v>0.0079965406332553387</v>
+        <v>0.0070436978462655809</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.038723359827467017</v>
       </c>
       <c r="B14">
-        <v>0.0083362362844000577</v>
+        <v>0.0073450321697164159</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.041702079814195249</v>
       </c>
       <c r="B15">
-        <v>0.0086302426623826329</v>
+        <v>0.0076058806382240862</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.044680799800923481</v>
       </c>
       <c r="B16">
-        <v>0.0088789180943824181</v>
+        <v>0.007826516151610589</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.047659519787651712</v>
       </c>
       <c r="B17">
-        <v>0.0090826209075787669</v>
+        <v>0.00800721160969792</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.050638239774379951</v>
       </c>
       <c r="B18">
-        <v>0.0092415897333775684</v>
+        <v>0.0081481496836890675</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.053616959761108175</v>
       </c>
       <c r="B19">
-        <v>0.0093555844200908633</v>
+        <v>0.0082491521303109921</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.056595679747836414</v>
       </c>
       <c r="B20">
-        <v>0.0094242451202572186</v>
+        <v>0.0083099504776716487</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.059574399734564638</v>
       </c>
       <c r="B21">
-        <v>0.00944721198641521</v>
+        <v>0.0083302762538789883</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.062553119721292877</v>
       </c>
       <c r="B22">
-        <v>0.0094242451202572186</v>
+        <v>0.0083099504776716487</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.065531839708021108</v>
       </c>
       <c r="B23">
-        <v>0.0093555844200908633</v>
+        <v>0.0082491521303109921</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.06851055969474934</v>
       </c>
       <c r="B24">
-        <v>0.0092415897333775684</v>
+        <v>0.0081481496836890675</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.071489279681477572</v>
       </c>
       <c r="B25">
-        <v>0.0090826209075787669</v>
+        <v>0.00800721160969792</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.0744679996682058</v>
       </c>
       <c r="B26">
-        <v>0.0088789180943824181</v>
+        <v>0.007826516151610589</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.077446719654934035</v>
       </c>
       <c r="B27">
-        <v>0.0086302426623826329</v>
+        <v>0.0076058806382240853</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.080425439641662266</v>
       </c>
       <c r="B28">
-        <v>0.0083362362844000559</v>
+        <v>0.0073450321697164141</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.0834041596283905</v>
       </c>
       <c r="B29">
-        <v>0.007996540633255337</v>
+        <v>0.0070436978462655783</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.086382879615118729</v>
       </c>
       <c r="B30">
-        <v>0.0076107999207575662</v>
+        <v>0.0067016062327989066</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.089361599601846961</v>
       </c>
       <c r="B31">
-        <v>0.0071786685146696307</v>
+        <v>0.0063184917532410154</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.092340319588575193</v>
       </c>
       <c r="B32">
-        <v>0.0066998033217428544</v>
+        <v>0.00589409029626584</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.095319039575303424</v>
       </c>
       <c r="B33">
-        <v>0.0061738612487285682</v>
+        <v>0.00542813775054732</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.098297759562031656</v>
       </c>
       <c r="B34">
-        <v>0.0055995240587512736</v>
+        <v>0.0049196383308847593</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.1012764795487599</v>
       </c>
       <c r="B35">
-        <v>0.0049715729404281577</v>
+        <v>0.0043646695565789234</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.10425519953548812</v>
       </c>
       <c r="B36">
-        <v>0.0042872345243894355</v>
+        <v>0.0037611426085817569</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.10723391952221635</v>
       </c>
       <c r="B37">
-        <v>0.0035574177838247241</v>
+        <v>0.0031172300099484465</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.11021263950894458</v>
       </c>
       <c r="B38">
-        <v>0.00279246023203458</v>
+        <v>0.00244067540986327</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.11319135949567283</v>
       </c>
       <c r="B39">
-        <v>0.00198673120020386</v>
+        <v>0.0017272456199235906</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.11617007948240106</v>
       </c>
       <c r="B40">
-        <v>0.0011306079739884984</v>
+        <v>0.0009697132423300449</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.11914879946912928</v>
       </c>
       <c r="B41">
-        <v>0.00021446783904443306</v>
+        <v>0.00016085087928327166</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.11914879946912928</v>
       </c>
       <c r="B42">
-        <v>-0.00021446783904443265</v>
+        <v>-0.00016085087928337751</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.11617007948240106</v>
       </c>
       <c r="B43">
-        <v>0.00026458262914028866</v>
+        <v>0.00032019423369388737</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.11319135949567283</v>
       </c>
       <c r="B44">
-        <v>0.00072851987780985633</v>
+        <v>0.00078358712812808819</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.11021263950894458</v>
       </c>
       <c r="B45">
-        <v>0.0011682756679779905</v>
+        <v>0.0012225369868208284</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.10723391952221635</v>
       </c>
       <c r="B46">
-        <v>0.0015747817606584129</v>
+        <v>0.0016302529925737136</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.10425519953548812</v>
       </c>
       <c r="B47">
-        <v>0.0019429454327140451</v>
+        <v>0.0020029257898252139</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.1012764795487599</v>
       </c>
       <c r="B48">
-        <v>0.0022835760244046027</v>
+        <v>0.002348671869561256</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.098297759562031656</v>
       </c>
       <c r="B49">
-        <v>0.0026080299798548843</v>
+        <v>0.0026760177717124667</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.095319039575303424</v>
       </c>
       <c r="B50">
-        <v>0.0029139500952531914</v>
+        <v>0.0029832043854407879</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.092340319588575193</v>
       </c>
       <c r="B51">
-        <v>0.0031965076624772535</v>
+        <v>0.0032666185518166395</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.089361599601846961</v>
       </c>
       <c r="B52">
-        <v>0.0034547016040989845</v>
+        <v>0.003525516570313031</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.086382879615118729</v>
       </c>
       <c r="B53">
-        <v>0.003688487750363843</v>
+        <v>0.0037598721050036135</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.0834041596283905</v>
       </c>
       <c r="B54">
-        <v>0.0038978219315172909</v>
+        <v>0.0039696588199620436</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.080425439641662266</v>
       </c>
       <c r="B55">
-        <v>0.0040826363464004593</v>
+        <v>0.0041548322162167153</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.077446719654934035</v>
       </c>
       <c r="B56">
-        <v>0.0042427686682371653</v>
+        <v>0.0043152751426149836</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.0744679996682058</v>
       </c>
       <c r="B57">
-        <v>0.0043780329388468974</v>
+        <v>0.004450852284958947</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.071489279681477572</v>
       </c>
       <c r="B58">
-        <v>0.0044882432000491424</v>
+        <v>0.0045614283290507</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.06851055969474934</v>
       </c>
       <c r="B59">
-        <v>0.0045733140408583447</v>
+        <v>0.0046469429142996493</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.065531839708021108</v>
       </c>
       <c r="B60">
-        <v>0.0046335622390687569</v>
+        <v>0.0047076354945444132</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.062553119721292877</v>
       </c>
       <c r="B61">
-        <v>0.0046694051196695865</v>
+        <v>0.0047438204772309251</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.059574399734564638</v>
       </c>
       <c r="B62">
-        <v>0.0046812600076500382</v>
+        <v>0.00475581226980511</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.056595679747836414</v>
       </c>
       <c r="B63">
-        <v>0.0046694051196695865</v>
+        <v>0.0047438204772309251</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.053616959761108175</v>
       </c>
       <c r="B64">
-        <v>0.0046335622390687569</v>
+        <v>0.0047076354945444132</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.050638239774379951</v>
       </c>
       <c r="B65">
-        <v>0.0045733140408583456</v>
+        <v>0.0046469429142996493</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.047659519787651712</v>
       </c>
       <c r="B66">
-        <v>0.0044882432000491433</v>
+        <v>0.0045614283290507009</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.044680799800923481</v>
       </c>
       <c r="B67">
-        <v>0.0043780329388468974</v>
+        <v>0.004450852284958947</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.041702079814195249</v>
       </c>
       <c r="B68">
-        <v>0.0042427686682371662</v>
+        <v>0.0043152751426149844</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.038723359827467017</v>
       </c>
       <c r="B69">
-        <v>0.00408263634640046</v>
+        <v>0.0041548322162167162</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.035744639840738786</v>
       </c>
       <c r="B70">
-        <v>0.0038978219315172927</v>
+        <v>0.0039696588199620454</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.032765919854010554</v>
       </c>
       <c r="B71">
-        <v>0.0036884877503638438</v>
+        <v>0.0037598721050036144</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.029787199867282319</v>
       </c>
       <c r="B72">
-        <v>0.0034547016040989836</v>
+        <v>0.00352551657031303</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.026808479880554088</v>
       </c>
       <c r="B73">
-        <v>0.0031965076624772531</v>
+        <v>0.0032666185518166395</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.023829759893825856</v>
       </c>
       <c r="B74">
-        <v>0.0029139500952531914</v>
+        <v>0.0029832043854407879</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.020851039907097624</v>
       </c>
       <c r="B75">
-        <v>0.0026080299798548852</v>
+        <v>0.002676017771712468</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.017872319920369393</v>
       </c>
       <c r="B76">
-        <v>0.0022835760244046049</v>
+        <v>0.0023486718695612582</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.01489359993364116</v>
       </c>
       <c r="B77">
-        <v>0.0019429454327140451</v>
+        <v>0.0020029257898252139</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.011914879946912928</v>
       </c>
       <c r="B78">
-        <v>0.0015747817606584129</v>
+        <v>0.0016302529925737136</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0089361599601846965</v>
       </c>
       <c r="B79">
-        <v>0.0011682756679779914</v>
+        <v>0.001222536986820829</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.005957439973456464</v>
       </c>
       <c r="B80">
-        <v>0.00072851987780985839</v>
+        <v>0.00078358712812809015</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.002978719986728232</v>
       </c>
       <c r="B81">
-        <v>0.00026458262914029121</v>
+        <v>0.00032019423369389024</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-0.00021446783904443271</v>
+        <v>-0.00016085087928337743</v>
       </c>
     </row>
   </sheetData>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-5.919541422609695E-17</v>
+        <v>5.919541422609695E-17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0033324055681336548</v>
       </c>
       <c r="B2">
-        <v>0.0020660270335666414</v>
+        <v>0.0019970697148990546</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.00666481113626731</v>
       </c>
       <c r="B3">
-        <v>0.0031813773700707323</v>
+        <v>0.0031866057393561019</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0099972167044009661</v>
       </c>
       <c r="B4">
-        <v>0.0041379696603123925</v>
+        <v>0.0042287368054872623</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.013329622272534619</v>
       </c>
       <c r="B5">
-        <v>0.0049799222706308445</v>
+        <v>0.0051604112880746658</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.016662027840668274</v>
       </c>
       <c r="B6">
-        <v>0.0057252786092581989</v>
+        <v>0.0059968361928202166</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.019994433408801932</v>
       </c>
       <c r="B7">
-        <v>0.0063843717099982527</v>
+        <v>0.006746777961945438</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.023326838976935587</v>
       </c>
       <c r="B8">
-        <v>0.00696331015865645</v>
+        <v>0.0074154752336716527</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.026659244545069238</v>
       </c>
       <c r="B9">
-        <v>0.0074715860189030221</v>
+        <v>0.0080109701510481263</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.029991650113202893</v>
       </c>
       <c r="B10">
-        <v>0.0079194369981370871</v>
+        <v>0.0085419185874452269</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.033324055681336548</v>
       </c>
       <c r="B11">
-        <v>0.0083166999008085375</v>
+        <v>0.009016627832689807</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0366564612494702</v>
       </c>
       <c r="B12">
-        <v>0.00866865216215256</v>
+        <v>0.0094395986648495717</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.039988866817603864</v>
       </c>
       <c r="B13">
-        <v>0.00896273464349473</v>
+        <v>0.0098004543984991366</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.043321272385737512</v>
       </c>
       <c r="B14">
-        <v>0.0091914532979516534</v>
+        <v>0.010093032310173437</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.046653677953871174</v>
       </c>
       <c r="B15">
-        <v>0.0093854110197136558</v>
+        <v>0.010342902987741754</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.049986083522004822</v>
       </c>
       <c r="B16">
-        <v>0.0095726765379472948</v>
+        <v>0.010573519302192672</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.053318489090138477</v>
       </c>
       <c r="B17">
-        <v>0.0097330849806503018</v>
+        <v>0.01076812994565768</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.056650894658272138</v>
       </c>
       <c r="B18">
-        <v>0.0098405826975587647</v>
+        <v>0.010905068755890661</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.059983300226405786</v>
       </c>
       <c r="B19">
-        <v>0.0098937945265310072</v>
+        <v>0.010983214331992152</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.063315705794539448</v>
       </c>
       <c r="B20">
-        <v>0.0098975149274559034</v>
+        <v>0.011006581463399352</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.0666481113626731</v>
       </c>
       <c r="B21">
-        <v>0.0098565383602223361</v>
+        <v>0.01097918493954946</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.069980516930806758</v>
       </c>
       <c r="B22">
-        <v>0.00977480393502363</v>
+        <v>0.010904320415566101</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.0733129224989404</v>
       </c>
       <c r="B23">
-        <v>0.00965282936327092</v>
+        <v>0.01078240700931858</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.076645328067074067</v>
       </c>
       <c r="B24">
-        <v>0.009490277006679794</v>
+        <v>0.010613144704362625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.079977733635207729</v>
       </c>
       <c r="B25">
-        <v>0.00928680922696584</v>
+        <v>0.010396233484253965</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.083310139203341377</v>
       </c>
       <c r="B26">
-        <v>0.0090419439836495578</v>
+        <v>0.010131246783815568</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.086642544771475025</v>
       </c>
       <c r="B27">
-        <v>0.0087546216274711035</v>
+        <v>0.009817251842939358</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.089974950339608686</v>
       </c>
       <c r="B28">
-        <v>0.0084236381069755437</v>
+        <v>0.0094531893527844985</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.093307355907742348</v>
       </c>
       <c r="B29">
-        <v>0.00804778937070795</v>
+        <v>0.0090380000045101536</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.096639761475876</v>
       </c>
       <c r="B30">
-        <v>0.00762650110640536</v>
+        <v>0.00857114268309551</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.099972167044009644</v>
       </c>
       <c r="B31">
-        <v>0.0071617179585726776</v>
+        <v>0.0080541490487998513</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.10330457261214331</v>
       </c>
       <c r="B32">
-        <v>0.0066560143109067639</v>
+        <v>0.0074890689557024744</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.10663697818027695</v>
       </c>
       <c r="B33">
-        <v>0.0061119645471044912</v>
+        <v>0.0068779522578826819</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.10996938374841062</v>
       </c>
       <c r="B34">
-        <v>0.0055311138591239584</v>
+        <v>0.0062219836428454066</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.11330178931654428</v>
       </c>
       <c r="B35">
-        <v>0.0049108906719681983</v>
+        <v>0.005518887131798096</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.11663419488467791</v>
       </c>
       <c r="B36">
-        <v>0.0042476942189014757</v>
+        <v>0.0047655215793738284</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.11996660045281157</v>
       </c>
       <c r="B37">
-        <v>0.00353792373318805</v>
+        <v>0.00395874584020567</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.12329900602094523</v>
       </c>
       <c r="B38">
-        <v>0.0027754614773241757</v>
+        <v>0.0030933137984773956</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.1266314115890789</v>
       </c>
       <c r="B39">
-        <v>0.0019441218307340656</v>
+        <v>0.0021555594565755452</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.12996381715721256</v>
       </c>
       <c r="B40">
-        <v>0.0010252022020739188</v>
+        <v>0.0011297118464373528</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.13329622272534619</v>
       </c>
       <c r="B41">
-        <v>-5.9426646312917646E-17</v>
+        <v>5.8732950052455571E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.13329622272534619</v>
       </c>
       <c r="B42">
-        <v>-5.919541422609695E-17</v>
+        <v>5.93110302695073E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.12996381715721256</v>
       </c>
       <c r="B43">
-        <v>0.00014767101294385269</v>
+        <v>0.00039843585549563114</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.1266314115890789</v>
       </c>
       <c r="B44">
-        <v>0.000339768494011802</v>
+        <v>0.00081859834264032521</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.12329900602094523</v>
       </c>
       <c r="B45">
-        <v>0.00055785437477170953</v>
+        <v>0.0012453078796836731</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.11996660045281157</v>
       </c>
       <c r="B46">
-        <v>0.000783490586791496</v>
+        <v>0.0016633848848752087</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.11663419488467791</v>
       </c>
       <c r="B47">
-        <v>0.0010007461921245485</v>
+        <v>0.0020597315570597217</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.11330178931654428</v>
       </c>
       <c r="B48">
-        <v>0.0012037187747661149</v>
+        <v>0.0024295772174630272</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.10996938374841062</v>
       </c>
       <c r="B49">
-        <v>0.001389013049196911</v>
+        <v>0.0027702329679062014</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.10663697818027695</v>
       </c>
       <c r="B50">
-        <v>0.0015532337298976506</v>
+        <v>0.0030790099102103157</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.10330457261214331</v>
       </c>
       <c r="B51">
-        <v>0.0016940042694561387</v>
+        <v>0.0033540605878269532</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.099972167044009644</v>
       </c>
       <c r="B52">
-        <v>0.0018130230728885431</v>
+        <v>0.0035969033107297404</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.096639761475876</v>
       </c>
       <c r="B53">
-        <v>0.0019130072833181226</v>
+        <v>0.003809897830522812</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.093307355907742348</v>
       </c>
       <c r="B54">
-        <v>0.0019966740438681369</v>
+        <v>0.0039954038988103081</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.089974950339608686</v>
       </c>
       <c r="B55">
-        <v>0.0020661010901786604</v>
+        <v>0.004155241838787095</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.086642544771475025</v>
       </c>
       <c r="B56">
-        <v>0.0021208085279570371</v>
+        <v>0.0042890742600109688</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.083310139203341377</v>
       </c>
       <c r="B57">
-        <v>0.002159677055427427</v>
+        <v>0.0043960243436304575</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.079977733635207729</v>
       </c>
       <c r="B58">
-        <v>0.0021815873708139893</v>
+        <v>0.0044752152707940871</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.076645328067074067</v>
       </c>
       <c r="B59">
-        <v>0.0021855551924068288</v>
+        <v>0.0045258765258018169</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.0733129224989404</v>
       </c>
       <c r="B60">
-        <v>0.0021711363187598216</v>
+        <v>0.0045476628055593294</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.069980516930806758</v>
       </c>
       <c r="B61">
-        <v>0.0021380215684927905</v>
+        <v>0.0045403351101237343</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.0666481113626731</v>
       </c>
       <c r="B62">
-        <v>0.0020859017602255551</v>
+        <v>0.0045036544395521422</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.063315705794539448</v>
       </c>
       <c r="B63">
-        <v>0.002015313389102602</v>
+        <v>0.004438080181438266</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.059983300226405786</v>
       </c>
       <c r="B64">
-        <v>0.0019301756563670747</v>
+        <v>0.0043468652735222076</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.056650894658272138</v>
       </c>
       <c r="B65">
-        <v>0.0018352534397867817</v>
+        <v>0.0042339610410806749</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.053318489090138477</v>
       </c>
       <c r="B66">
-        <v>0.0017353116171295304</v>
+        <v>0.0041033188093903706</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.049986083522004822</v>
       </c>
       <c r="B67">
-        <v>0.00162893762748695</v>
+        <v>0.00395373687680905</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.046653677953871174</v>
       </c>
       <c r="B68">
-        <v>0.0014900091552459511</v>
+        <v>0.0037634014340186643</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.043321272385737512</v>
       </c>
       <c r="B69">
-        <v>0.0012982813242759803</v>
+        <v>0.0035153889987770441</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.039988866817603864</v>
       </c>
       <c r="B70">
-        <v>0.0010817287710813614</v>
+        <v>0.0032329495048213294</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0366564612494702</v>
       </c>
       <c r="B71">
-        <v>0.00087085158172897246</v>
+        <v>0.0029414315144965803</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.033324055681336548</v>
       </c>
       <c r="B72">
-        <v>0.00065803212790104806</v>
+        <v>0.002634404688600231</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.029991650113202893</v>
       </c>
       <c r="B73">
-        <v>0.00043057761005069065</v>
+        <v>0.002301202430706562</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.026659244545069238</v>
       </c>
       <c r="B74">
-        <v>0.00019361225809911932</v>
+        <v>0.001945992017044873</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.023326838976935587</v>
       </c>
       <c r="B75">
-        <v>-4.319028185246228E-05</v>
+        <v>0.001576724866580892</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.019994433408801932</v>
       </c>
       <c r="B76">
-        <v>-0.00026977572845102903</v>
+        <v>0.0012016550965710362</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.016662027840668274</v>
       </c>
       <c r="B77">
-        <v>-0.00047684593774636335</v>
+        <v>0.00082839907031641443</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.013329622272534619</v>
       </c>
       <c r="B78">
-        <v>-0.00065850795065129847</v>
+        <v>0.00046171943700621288</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0099972167044009661</v>
       </c>
       <c r="B79">
-        <v>-0.00080465427834344413</v>
+        <v>0.00010988352327406461</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.00666481113626731</v>
       </c>
       <c r="B80">
-        <v>-0.00089748704532485984</v>
+        <v>-0.00021244794014022529</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0033324055681336548</v>
       </c>
       <c r="B81">
-        <v>-0.00089314911093604343</v>
+        <v>-0.00046891040551984964</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-5.919541422609695E-17</v>
+        <v>5.919541422609695E-17</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>2.5398094181198004E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0035744639840738779</v>
       </c>
       <c r="B2">
-        <v>0.0023290092829566511</v>
+        <v>0.0027269298654885648</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0071489279681477558</v>
       </c>
       <c r="B3">
-        <v>0.0033316606991494525</v>
+        <v>0.00425551462144535</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.010723391952221635</v>
       </c>
       <c r="B4">
-        <v>0.0041403501091712026</v>
+        <v>0.00557700612090143</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.014297855936295512</v>
       </c>
       <c r="B5">
-        <v>0.0048179934385684442</v>
+        <v>0.0067468339334905937</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.017872319920369389</v>
       </c>
       <c r="B6">
-        <v>0.005390225563244898</v>
+        <v>0.0077877817912925928</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.021446783904443271</v>
       </c>
       <c r="B7">
-        <v>0.0058716680206189285</v>
+        <v>0.0087129656172133217</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.025021247888517149</v>
       </c>
       <c r="B8">
-        <v>0.0062709075123713147</v>
+        <v>0.0095302056470296728</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.028595711872591023</v>
       </c>
       <c r="B9">
-        <v>0.0066013848331820963</v>
+        <v>0.01025153653011498</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0321701758566649</v>
       </c>
       <c r="B10">
-        <v>0.0068776144811081089</v>
+        <v>0.010889916713956574</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.035744639840738779</v>
       </c>
       <c r="B11">
-        <v>0.0071135516747140989</v>
+        <v>0.011457785424901334</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.039319103824812657</v>
       </c>
       <c r="B12">
-        <v>0.0073166378122263764</v>
+        <v>0.011961867782167656</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.042893567808886542</v>
       </c>
       <c r="B13">
-        <v>0.0074688182900096182</v>
+        <v>0.01238655169760039</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.046468031792960413</v>
       </c>
       <c r="B14">
-        <v>0.0075592895142571432</v>
+        <v>0.012722555333541604</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0500424957770343</v>
       </c>
       <c r="B15">
-        <v>0.0076317479323384741</v>
+        <v>0.013008255061695733</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.053616959761108168</v>
       </c>
       <c r="B16">
-        <v>0.0077262717191086535</v>
+        <v>0.013278848995732022</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.057191423745182046</v>
       </c>
       <c r="B17">
-        <v>0.007813965918188566</v>
+        <v>0.013509164007816566</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.060765887729255931</v>
       </c>
       <c r="B18">
-        <v>0.0078575214043307764</v>
+        <v>0.013666648878330289</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.0643403517133298</v>
       </c>
       <c r="B19">
-        <v>0.00785494550804871</v>
+        <v>0.013749611262016554</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.06791481569740368</v>
       </c>
       <c r="B20">
-        <v>0.0078130746737960048</v>
+        <v>0.013764073532209339</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.071489279681477558</v>
       </c>
       <c r="B21">
-        <v>0.0077387453460263048</v>
+        <v>0.013716058062242617</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.075063743665551436</v>
       </c>
       <c r="B22">
-        <v>0.0076375773698235932</v>
+        <v>0.013610509467754812</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.078638207649625314</v>
       </c>
       <c r="B23">
-        <v>0.0075103241927932263</v>
+        <v>0.013448061333602141</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.0822126716336992</v>
       </c>
       <c r="B24">
-        <v>0.0073565226631709052</v>
+        <v>0.013228269486945271</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.085787135617773083</v>
       </c>
       <c r="B25">
-        <v>0.0071757096291923334</v>
+        <v>0.01295068975494486</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.089361599601846947</v>
       </c>
       <c r="B26">
-        <v>0.0069672219250352463</v>
+        <v>0.01261469000972253</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.092936063585920825</v>
       </c>
       <c r="B27">
-        <v>0.0067295963286455257</v>
+        <v>0.012218886303243677</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.0965105275699947</v>
       </c>
       <c r="B28">
-        <v>0.0064611696039110871</v>
+        <v>0.011761706732434664</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.1000849915540686</v>
       </c>
       <c r="B29">
-        <v>0.0061602785147198517</v>
+        <v>0.011241579394221844</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.10365945553814247</v>
       </c>
       <c r="B30">
-        <v>0.005826167178626932</v>
+        <v>0.010657712656904014</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.10723391952221634</v>
       </c>
       <c r="B31">
-        <v>0.0054617091278562355</v>
+        <v>0.010012435974269736</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.11080838350629021</v>
       </c>
       <c r="B32">
-        <v>0.005070685248298859</v>
+        <v>0.0093088590714800017</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.11438284749036409</v>
       </c>
       <c r="B33">
-        <v>0.0046568764258459062</v>
+        <v>0.0085500916736958137</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.11795731147443798</v>
       </c>
       <c r="B34">
-        <v>0.0042225988787856182</v>
+        <v>0.0077379464732646765</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.12153177545851186</v>
       </c>
       <c r="B35">
-        <v>0.0037643101549947829</v>
+        <v>0.0068690480312801052</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.12510623944258573</v>
       </c>
       <c r="B36">
-        <v>0.0032770031347473297</v>
+        <v>0.0059387238760221211</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.1286807034266596</v>
       </c>
       <c r="B37">
-        <v>0.0027556706983171806</v>
+        <v>0.0049423015357707382</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.13225516741073348</v>
       </c>
       <c r="B38">
-        <v>0.0021917128447868908</v>
+        <v>0.0038719494623929828</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.13582963139480736</v>
       </c>
       <c r="B39">
-        <v>0.0015621580484735174</v>
+        <v>0.0027071998021039041</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.13940409537888124</v>
       </c>
       <c r="B40">
-        <v>0.00084044190250274283</v>
+        <v>0.0014244256247055562</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.14297855936295512</v>
       </c>
       <c r="B41">
-        <v>2.5373291354849179E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.14297855936295512</v>
       </c>
       <c r="B42">
-        <v>2.5398094181198004E-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.13940409537888124</v>
       </c>
       <c r="B43">
-        <v>-0.00041458886183633881</v>
+        <v>0.00032627370590886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.13582963139480736</v>
       </c>
       <c r="B44">
-        <v>-0.000732361872183182</v>
+        <v>0.00069949487152929214</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.13225516741073348</v>
       </c>
       <c r="B45">
-        <v>-0.00097987258875110984</v>
+        <v>0.001096812208047232</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.1286807034266596</v>
       </c>
       <c r="B46">
-        <v>-0.0011836745692509589</v>
+        <v>0.0014953744266486158</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.12510623944258573</v>
       </c>
       <c r="B47">
-        <v>-0.0013667288650860427</v>
+        <v>0.0018754583761679208</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.12153177545851186</v>
       </c>
       <c r="B48">
-        <v>-0.0015376265024295843</v>
+        <v>0.0022298534560337836</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.11795731147443798</v>
       </c>
       <c r="B49">
-        <v>-0.0017013660011472858</v>
+        <v>0.0025544772033233853</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.11438284749036409</v>
       </c>
       <c r="B50">
-        <v>-0.0018629458811048475</v>
+        <v>0.0028452471551139043</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.11080838350629021</v>
       </c>
       <c r="B51">
-        <v>-0.0020259004139766166</v>
+        <v>0.0030993466169889597</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.10723391952221634</v>
       </c>
       <c r="B52">
-        <v>-0.0021879068786715278</v>
+        <v>0.0033190219685579427</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.10365945553814247</v>
       </c>
       <c r="B53">
-        <v>-0.0023451783059071593</v>
+        <v>0.0035077853579366831</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.1000849915540686</v>
       </c>
       <c r="B54">
-        <v>-0.0024939277264010937</v>
+        <v>0.0036691489332410163</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.0965105275699947</v>
       </c>
       <c r="B55">
-        <v>-0.0026312759300356008</v>
+        <v>0.003805816890231311</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.092936063585920825</v>
       </c>
       <c r="B56">
-        <v>-0.0027579747433517095</v>
+        <v>0.0039172616152460963</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.089361599601846947</v>
       </c>
       <c r="B57">
-        <v>-0.00287568375205514</v>
+        <v>0.0040021475422684395</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.085787135617773083</v>
       </c>
       <c r="B58">
-        <v>-0.0029860625418516107</v>
+        <v>0.0040591391052814093</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.0822126716336992</v>
       </c>
       <c r="B59">
-        <v>-0.0030905710873539547</v>
+        <v>0.0040870624552360154</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.078638207649625314</v>
       </c>
       <c r="B60">
-        <v>-0.0031898709188034518</v>
+        <v>0.0040853906109550473</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.075063743665551436</v>
       </c>
       <c r="B61">
-        <v>-0.0032844239553484924</v>
+        <v>0.0040537583082292357</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.071489279681477558</v>
       </c>
       <c r="B62">
-        <v>-0.0033746921161374693</v>
+        <v>0.0039918002828493119</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.06791481569740368</v>
       </c>
       <c r="B63">
-        <v>-0.0034599211397898237</v>
+        <v>0.0039002021953217351</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.0643403517133298</v>
       </c>
       <c r="B64">
-        <v>-0.0035344920428092056</v>
+        <v>0.0037838534050158765</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.060765887729255931</v>
       </c>
       <c r="B65">
-        <v>-0.0035915696611703123</v>
+        <v>0.0036486941960168343</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.057191423745182046</v>
       </c>
       <c r="B66">
-        <v>-0.0036243188308478433</v>
+        <v>0.0035006648524097063</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.053616959761108168</v>
       </c>
       <c r="B67">
-        <v>-0.0036347338382989097</v>
+        <v>0.0033379691330004029</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0500424957770343</v>
       </c>
       <c r="B68">
-        <v>-0.0036601267719102693</v>
+        <v>0.0031278646954780824</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.046468031792960413</v>
       </c>
       <c r="B69">
-        <v>-0.0037293960366261312</v>
+        <v>0.0028449554765187395</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.042893567808886542</v>
       </c>
       <c r="B70">
-        <v>-0.0038024675016908589</v>
+        <v>0.0025241766298624737</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.039319103824812657</v>
       </c>
       <c r="B71">
-        <v>-0.0038356491307761859</v>
+        <v>0.0022036167070404156</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.035744639840738779</v>
       </c>
       <c r="B72">
-        <v>-0.0038397498009631664</v>
+        <v>0.0018736466336837295</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0321701758566649</v>
       </c>
       <c r="B73">
-        <v>-0.0038328298179433626</v>
+        <v>0.0015182779522865352</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.028595711872591023</v>
       </c>
       <c r="B74">
-        <v>-0.0038074542884410367</v>
+        <v>0.0011438022986947382</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.025021247888517149</v>
       </c>
       <c r="B75">
-        <v>-0.0037496749035212254</v>
+        <v>0.0007621960331237</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.021446783904443271</v>
       </c>
       <c r="B76">
-        <v>-0.0036449848905793633</v>
+        <v>0.00038589431991481563</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.017872319920369389</v>
       </c>
       <c r="B77">
-        <v>-0.0034799515964635593</v>
+        <v>2.6376776547692688E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.014297855936295512</v>
       </c>
       <c r="B78">
-        <v>-0.0032459973095022229</v>
+        <v>-0.00030915797107123992</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.010723391952221635</v>
       </c>
       <c r="B79">
-        <v>-0.0029285098657332986</v>
+        <v>-0.00060824635714000974</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0071489279681477558</v>
       </c>
       <c r="B80">
-        <v>-0.0025018645228591153</v>
+        <v>-0.0008488199478121467</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0035744639840738779</v>
       </c>
       <c r="B81">
-        <v>-0.0019031560741868204</v>
+        <v>-0.00097621482201197345</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>2.5398094181198004E-16</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
